--- a/data/trans_bre/PCS12_SP_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R2-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 11,61</t>
+          <t>0,67; 11,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 9,94</t>
+          <t>-2,04; 9,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 9,14</t>
+          <t>-2,18; 9,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 8,31</t>
+          <t>-10,83; 8,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 60,01</t>
+          <t>2,2; 57,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 46,17</t>
+          <t>-7,63; 44,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 58,03</t>
+          <t>-10,98; 58,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 65,35</t>
+          <t>-44,39; 60,28</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 21,07</t>
+          <t>10,59; 21,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 13,28</t>
+          <t>1,18; 12,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 6,71</t>
+          <t>-3,81; 6,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 3,08</t>
+          <t>-16,77; 2,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,0; 98,83</t>
+          <t>39,02; 98,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 52,37</t>
+          <t>3,83; 48,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 35,82</t>
+          <t>-15,2; 33,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 10,44</t>
+          <t>-47,53; 9,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 19,13</t>
+          <t>9,22; 19,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 14,15</t>
+          <t>3,42; 13,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 15,18</t>
+          <t>4,89; 15,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 8,27</t>
+          <t>-2,63; 8,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,34; 61,21</t>
+          <t>24,27; 61,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 41,86</t>
+          <t>8,73; 43,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,68; 69,29</t>
+          <t>19,04; 71,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 26,71</t>
+          <t>-7,39; 25,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,73; 23,77</t>
+          <t>12,03; 23,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 15,11</t>
+          <t>2,67; 14,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 11,0</t>
+          <t>-0,49; 11,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 5,59</t>
+          <t>-34,5; 6,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,44; 60,91</t>
+          <t>26,38; 62,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 39,22</t>
+          <t>6,03; 38,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 31,7</t>
+          <t>-0,91; 32,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 11,87</t>
+          <t>-41,57; 13,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 10,69</t>
+          <t>-2,55; 10,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 18,57</t>
+          <t>5,13; 17,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 12,88</t>
+          <t>0,05; 13,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 10,73</t>
+          <t>0,2; 10,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 17,01</t>
+          <t>-3,71; 17,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 33,86</t>
+          <t>8,0; 31,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 24,35</t>
+          <t>-0,05; 25,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 19,31</t>
+          <t>0,35; 18,25</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,32; 16,67</t>
+          <t>5,21; 16,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 11,98</t>
+          <t>-1,2; 11,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 15,31</t>
+          <t>1,84; 16,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,79; 33,35</t>
+          <t>11,83; 33,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 23,06</t>
+          <t>6,35; 23,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 16,62</t>
+          <t>-1,59; 16,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 23,49</t>
+          <t>2,59; 25,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,44; 57,25</t>
+          <t>18,66; 56,82</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 10,4</t>
+          <t>0,54; 9,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 12,25</t>
+          <t>2,24; 12,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,71</t>
+          <t>3,6; 14,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 15,42</t>
+          <t>7,52; 15,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 11,99</t>
+          <t>0,58; 11,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 14,72</t>
+          <t>2,43; 15,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 18,73</t>
+          <t>4,37; 18,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 20,03</t>
+          <t>9,11; 20,1</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,81</t>
+          <t>11,92; 16,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,92</t>
+          <t>7,89; 12,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,13</t>
+          <t>6,49; 11,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 12,41</t>
+          <t>-5,72; 12,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,35; 40,73</t>
+          <t>27,33; 41,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,15; 30,35</t>
+          <t>17,5; 30,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,88; 29,5</t>
+          <t>16,09; 29,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 25,91</t>
+          <t>-11,39; 26,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/PCS12_SP_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,01%</t>
+          <t>-2,85%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 11,38</t>
+          <t>0,22; 11,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 9,63</t>
+          <t>-1,7; 10,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 9,01</t>
+          <t>-2,05; 8,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 8,33</t>
+          <t>-9,13; 7,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 57,14</t>
+          <t>-0,32; 59,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 44,91</t>
+          <t>-6,38; 48,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 58,22</t>
+          <t>-9,62; 58,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 60,28</t>
+          <t>-37,56; 49,51</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,66</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,3%</t>
+          <t>-3,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 21,0</t>
+          <t>10,05; 20,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 12,27</t>
+          <t>1,53; 11,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 6,26</t>
+          <t>-3,73; 6,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 2,7</t>
+          <t>-8,01; 6,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,02; 98,86</t>
+          <t>39,13; 97,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 48,37</t>
+          <t>4,9; 47,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 33,09</t>
+          <t>-15,38; 32,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 9,97</t>
+          <t>-23,27; 23,97</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,22; 19,61</t>
+          <t>8,76; 19,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 13,96</t>
+          <t>3,28; 13,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 15,24</t>
+          <t>5,28; 15,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 8,2</t>
+          <t>-1,4; 8,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,27; 61,79</t>
+          <t>23,85; 63,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,73; 43,2</t>
+          <t>8,01; 40,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,04; 71,72</t>
+          <t>19,71; 70,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 25,87</t>
+          <t>-3,58; 28,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,5</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,05%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 23,83</t>
+          <t>11,21; 23,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 14,53</t>
+          <t>3,13; 15,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 11,17</t>
+          <t>-0,43; 10,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 6,36</t>
+          <t>0,58; 10,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,38; 62,22</t>
+          <t>24,55; 58,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 38,18</t>
+          <t>6,99; 40,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 32,29</t>
+          <t>-1,28; 30,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 13,7</t>
+          <t>1,1; 24,26</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 10,99</t>
+          <t>-2,43; 10,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 17,56</t>
+          <t>5,03; 18,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 13,12</t>
+          <t>-0,2; 13,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 10,16</t>
+          <t>1,78; 11,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 17,31</t>
+          <t>-3,39; 17,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 31,93</t>
+          <t>7,68; 34,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 25,05</t>
+          <t>-0,22; 25,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 18,25</t>
+          <t>2,93; 20,93</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21,26</t>
+          <t>13,75</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 16,94</t>
+          <t>4,9; 17,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 11,65</t>
+          <t>-1,41; 11,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 16,17</t>
+          <t>1,69; 15,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,83; 33,64</t>
+          <t>8,76; 18,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,35; 23,07</t>
+          <t>6,01; 23,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 16,07</t>
+          <t>-1,69; 15,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 25,38</t>
+          <t>2,6; 24,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,66; 56,82</t>
+          <t>13,28; 31,34</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,22</t>
+          <t>11,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 9,89</t>
+          <t>1,11; 9,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 12,89</t>
+          <t>2,35; 12,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 14,64</t>
+          <t>3,89; 14,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 15,52</t>
+          <t>7,64; 15,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 11,45</t>
+          <t>1,18; 11,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 15,34</t>
+          <t>2,63; 15,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 18,96</t>
+          <t>4,69; 19,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,11; 20,1</t>
+          <t>9,08; 20,82</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,92; 16,96</t>
+          <t>12,04; 16,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,75</t>
+          <t>7,93; 12,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,25</t>
+          <t>6,31; 11,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 12,23</t>
+          <t>5,03; 10,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,33; 41,75</t>
+          <t>27,23; 41,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,5; 30,03</t>
+          <t>17,39; 29,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,09; 29,91</t>
+          <t>15,74; 29,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 26,23</t>
+          <t>10,88; 22,7</t>
         </is>
       </c>
     </row>
